--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484178_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484178_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3094</v>
+        <v>7.6417</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3197</v>
+        <v>7.7989</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0103</v>
+        <v>-0.1571</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7575</v>
+        <v>8.670199999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.306</v>
+        <v>3.0943</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4514</v>
+        <v>5.576</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9297</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6273</v>
+        <v>3.6747</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3024</v>
+        <v>5.0253</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1723</v>
+        <v>-0.0298</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3213</v>
+        <v>-0.5804</v>
       </c>
       <c r="O2" t="n">
-        <v>0.149</v>
+        <v>0.5507</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4924</v>
+        <v>0.6702</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5839</v>
+        <v>0.7653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9085</v>
+        <v>-0.095</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3373</v>
+        <v>-3.0874</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.6745</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1352</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4086</v>
+        <v>6.8755</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8183</v>
+        <v>7.1383</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4096</v>
+        <v>-0.2628</v>
       </c>
       <c r="G3" t="n">
-        <v>8.670199999999999</v>
+        <v>5.7575</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0943</v>
+        <v>1.306</v>
       </c>
       <c r="I3" t="n">
-        <v>5.576</v>
+        <v>4.4514</v>
       </c>
       <c r="J3" t="n">
-        <v>8.699999999999999</v>
+        <v>6.9297</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6747</v>
+        <v>2.6273</v>
       </c>
       <c r="L3" t="n">
-        <v>5.0253</v>
+        <v>4.3024</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0298</v>
+        <v>-1.1723</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5804</v>
+        <v>-1.3213</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5507</v>
+        <v>0.149</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5629</v>
+        <v>1.0585</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2153</v>
+        <v>0.4026</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3475</v>
+        <v>0.656</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.0874</v>
+        <v>-0.3373</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6745</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4129</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.649</v>
+        <v>6.3119</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2921</v>
+        <v>4.927</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3569</v>
+        <v>1.385</v>
       </c>
       <c r="G4" t="n">
         <v>3.4056</v>
@@ -766,13 +766,13 @@
         <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6728</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5611</v>
+        <v>0.0737</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1117</v>
+        <v>-0.0837</v>
       </c>
       <c r="V4" t="n">
         <v>0.3373</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2627</v>
+        <v>4.8119</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4243</v>
+        <v>3.9174</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8384</v>
+        <v>0.8945</v>
       </c>
       <c r="G5" t="n">
         <v>3.0411</v>
@@ -844,13 +844,13 @@
         <v>2.9758</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0282</v>
+        <v>-0.479</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7368</v>
+        <v>-0.2437</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2914</v>
+        <v>-0.2353</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2561</v>
+        <v>3.598</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2647</v>
+        <v>3.5505</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0086</v>
+        <v>0.0475</v>
       </c>
       <c r="G6" t="n">
         <v>0.3133</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>2.078</v>
+        <v>1.4199</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8989</v>
+        <v>1.1847</v>
       </c>
       <c r="U6" t="n">
-        <v>0.179</v>
+        <v>0.2352</v>
       </c>
       <c r="V6" t="n">
         <v>0.6745</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.9659</v>
+        <v>2.5545</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8549</v>
+        <v>1.6306</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1109</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>2.7982</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.477</v>
+        <v>1.0656</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0406</v>
+        <v>0.8162</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4364</v>
+        <v>0.2494</v>
       </c>
       <c r="V7" t="n">
         <v>0.6745</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7469</v>
+        <v>2.0235</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1024</v>
+        <v>1.3386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6444</v>
+        <v>0.6849</v>
       </c>
       <c r="G8" t="n">
-        <v>0.026</v>
+        <v>2.5573</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4132</v>
+        <v>0.4533</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4392</v>
+        <v>2.104</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4032</v>
+        <v>2.3361</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4393</v>
+        <v>1.0484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9639</v>
+        <v>1.2877</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3772</v>
+        <v>0.2212</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8525</v>
+        <v>-0.5951</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.8162</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3322</v>
+        <v>0.2678</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4252</v>
+        <v>-0.0056</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.093</v>
+        <v>0.2734</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4128</v>
+        <v>2.0208</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8681</v>
+        <v>1.7203</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5446</v>
+        <v>0.3005</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5573</v>
+        <v>0.3491</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4533</v>
+        <v>-0.2222</v>
       </c>
       <c r="I9" t="n">
-        <v>2.104</v>
+        <v>0.5713</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3361</v>
+        <v>1.0689</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0484</v>
+        <v>0.504</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2877</v>
+        <v>0.5648</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2212</v>
+        <v>-0.7197</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5951</v>
+        <v>-0.7262</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8162</v>
+        <v>0.0065</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3429</v>
+        <v>0.4138</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4761</v>
+        <v>0.3855</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1332</v>
+        <v>0.0283</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1842</v>
+        <v>1.5819</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1081</v>
+        <v>0.8814</v>
       </c>
       <c r="F10" t="n">
-        <v>0.076</v>
+        <v>0.7006</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3491</v>
+        <v>0.026</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2222</v>
+        <v>-0.4132</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5713</v>
+        <v>0.4392</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0689</v>
+        <v>1.4032</v>
       </c>
       <c r="K10" t="n">
-        <v>0.504</v>
+        <v>0.4393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5648</v>
+        <v>0.9639</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7197</v>
+        <v>-1.3772</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7262</v>
+        <v>-0.8525</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0065</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4228</v>
+        <v>0.1672</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2267</v>
+        <v>0.2041</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1961</v>
+        <v>-0.0369</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8274</v>
+        <v>1.4942</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2518</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5756</v>
+        <v>0.772</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3578</v>
@@ -1308,13 +1308,13 @@
         <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.997</v>
+        <v>-0.3302</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3117</v>
+        <v>0.1587</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6853</v>
+        <v>-0.4889</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1341,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8274</v>
+        <v>1.4942</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2518</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5756</v>
+        <v>0.772</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3578</v>
@@ -1386,13 +1386,13 @@
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.997</v>
+        <v>-0.3302</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3117</v>
+        <v>0.1587</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6853</v>
+        <v>-0.4889</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4001</v>
+        <v>-1.8924</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2886</v>
+        <v>-0.6967</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1115</v>
+        <v>-1.1957</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6307</v>
@@ -1464,13 +1464,13 @@
         <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6274</v>
+        <v>1.1351</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1337</v>
+        <v>0.7256</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4936</v>
+        <v>0.4095</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2065</v>
@@ -1485,7 +1485,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>N. ELIAS ALONSO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1497,64 +1497,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7216</v>
+        <v>-2.8995</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.688</v>
+        <v>-1.7833</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0336</v>
+        <v>-1.1161</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.015</v>
+        <v>-1.5226</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2294</v>
+        <v>-1.9151</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.7855</v>
+        <v>0.3926</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.6395</v>
+        <v>-0.5194</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6441</v>
+        <v>-0.6399</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.9953</v>
+        <v>0.1205</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3755</v>
+        <v>-1.0032</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5853</v>
+        <v>-1.2753</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7902</v>
+        <v>0.2721</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4918</v>
+        <v>-0.1785</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3402</v>
+        <v>-0.272</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1516</v>
+        <v>0.0935</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.6032</v>
@@ -1563,7 +1563,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. ELIAS ALONSO</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1575,64 +1575,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.12</v>
+        <v>-3.0061</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.9477</v>
+        <v>-2.5236</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1723</v>
+        <v>-0.4825</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5226</v>
+        <v>-4.015</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.9151</v>
+        <v>-1.2294</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3926</v>
+        <v>-2.7855</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5194</v>
+        <v>-2.6395</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6399</v>
+        <v>-0.6441</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1205</v>
+        <v>-1.9953</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0032</v>
+        <v>-1.3755</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2753</v>
+        <v>-0.5853</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2721</v>
+        <v>-0.7902</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.399</v>
+        <v>1.2073</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4364</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0374</v>
+        <v>0.7027</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X15" t="n">
         <v>-0.6032</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>30.60869999999998</v>
+        <v>32.61009999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>27.6319</v>
+        <v>29.34399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9765</v>
+        <v>3.266699999999999</v>
       </c>
       <c r="G16" t="n">
         <v>20.0344</v>
@@ -1686,7 +1686,7 @@
         <v>-11.8212</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5437000000000002</v>
+        <v>-0.5437000000000001</v>
       </c>
       <c r="P16" t="n">
         <v>10.1175</v>
@@ -1698,13 +1698,13 @@
         <v>21.0286</v>
       </c>
       <c r="S16" t="n">
-        <v>4.076199999999999</v>
+        <v>6.077600000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1467</v>
+        <v>4.8583</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9293999999999999</v>
+        <v>1.2193</v>
       </c>
       <c r="V16" t="n">
         <v>-3.6193</v>
@@ -1719,7 +1719,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,73 +1731,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2631</v>
+        <v>1.1052</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0946</v>
+        <v>2.8222</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8316</v>
+        <v>-1.717</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0804</v>
+        <v>-1.2108</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9574</v>
+        <v>-0.1861</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0378</v>
+        <v>-1.0247</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7671</v>
+        <v>1.6335</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6868</v>
+        <v>1.4728</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0803</v>
+        <v>0.1606</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8475</v>
+        <v>-2.8443</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7294</v>
+        <v>-1.659</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1181</v>
+        <v>-1.1853</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2759</v>
+        <v>-0.6802</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5498</v>
+        <v>-0.5497</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8257</v>
+        <v>-0.1304</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8692</v>
+        <v>1.8059</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8692</v>
+        <v>1.7384</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,73 +1809,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0249</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8439</v>
+        <v>2.5028</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.8688</v>
+        <v>-2.4207</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9794</v>
+        <v>-1.0804</v>
       </c>
       <c r="H18" t="n">
-        <v>3.871</v>
+        <v>0.9574</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8916</v>
+        <v>-2.0378</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6958</v>
+        <v>2.7671</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3333</v>
+        <v>2.6868</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6375</v>
+        <v>0.0803</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7164</v>
+        <v>-3.8475</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4622</v>
+        <v>-1.7294</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2542</v>
+        <v>-2.1181</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0799</v>
+        <v>0.0949</v>
       </c>
       <c r="T18" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.1416</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.148</v>
+        <v>0.2365</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0639</v>
+        <v>0.8692</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1887,73 +1887,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2858</v>
+        <v>-0.0427</v>
       </c>
       <c r="E19" t="n">
-        <v>2.312</v>
+        <v>3.7419</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5978</v>
+        <v>-3.7846</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2108</v>
+        <v>0.9794</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1861</v>
+        <v>3.871</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0247</v>
+        <v>-2.8916</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6335</v>
+        <v>4.6958</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4728</v>
+        <v>5.3333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1606</v>
+        <v>-0.6375</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8443</v>
+        <v>-3.7164</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.659</v>
+        <v>-1.4622</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1853</v>
+        <v>-2.2542</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1903</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0711</v>
+        <v>-0.0978</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0599</v>
+        <v>-0.0339</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0113</v>
+        <v>-0.0639</v>
       </c>
       <c r="V19" t="n">
-        <v>1.8059</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7384</v>
+        <v>1.0639</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0675</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. LAGUARDA ROQUEÑI</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0592</v>
+        <v>-0.4334</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3137</v>
+        <v>-0.5244</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7455000000000001</v>
+        <v>0.0911</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2594</v>
+        <v>-2.2231</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0955</v>
+        <v>-0.7863</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.355</v>
+        <v>-1.4368</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0603</v>
+        <v>-1.2491</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0202</v>
+        <v>0.0711</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>-1.3202</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3198</v>
+        <v>-0.9739</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3951</v>
+        <v>-0.1165</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9982</v>
+        <v>-0.6745</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3741</v>
+        <v>-0.4817</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6241</v>
+        <v>-0.1928</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2739</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>E. LAGUARDA ROQUEÑI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1816</v>
+        <v>-0.5669</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7285</v>
+        <v>-0.3137</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4531</v>
+        <v>-0.2532</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2231</v>
+        <v>-0.2594</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7863</v>
+        <v>0.0955</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4368</v>
+        <v>-0.355</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2491</v>
+        <v>0.0603</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0711</v>
+        <v>0.0202</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3202</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9739</v>
+        <v>-0.3198</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8574000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1165</v>
+        <v>-0.3951</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4227</v>
+        <v>-0.5059</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6858</v>
+        <v>-0.3741</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7369</v>
+        <v>-0.1318</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2739</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3727</v>
+        <v>-2.3692</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5193</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8919</v>
+        <v>-3.0925</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1842</v>
@@ -2166,13 +2166,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2516</v>
+        <v>0.2551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1189</v>
+        <v>0.0851</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3706</v>
+        <v>0.1699</v>
       </c>
       <c r="V22" t="n">
         <v>0.3373</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5463</v>
+        <v>-2.5506</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0318</v>
+        <v>-0.3763</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5782</v>
+        <v>-2.1743</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4688</v>
@@ -2244,13 +2244,13 @@
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0935</v>
+        <v>-0.0978</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3629</v>
+        <v>-0.0452</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4564</v>
+        <v>-0.0525</v>
       </c>
       <c r="V23" t="n">
         <v>1.0079</v>
@@ -2265,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,73 +2277,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7813</v>
+        <v>-3.1188</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5229</v>
+        <v>-1.6953</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2584</v>
+        <v>-1.4235</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9796</v>
+        <v>-2.8093</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4484</v>
+        <v>-0.761</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5312</v>
+        <v>-2.0482</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2876</v>
+        <v>-0.2387</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2876</v>
+        <v>0.3586</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2672</v>
+        <v>-2.5706</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.736</v>
+        <v>-1.1197</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5312</v>
+        <v>-1.4509</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4561</v>
+        <v>-0.5753</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1734</v>
+        <v>-0.4647</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2828</v>
+        <v>-0.1106</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4724</v>
+        <v>0.0675</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4724</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2355,67 +2355,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9911</v>
+        <v>-3.794</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1034</v>
+        <v>-1.3392</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8877</v>
+        <v>-2.4548</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8093</v>
+        <v>-0.9796</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.761</v>
+        <v>-0.4484</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0482</v>
+        <v>-0.5312</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2387</v>
+        <v>0.2876</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3586</v>
+        <v>0.2876</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5706</v>
+        <v>-1.2672</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1197</v>
+        <v>-0.736</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4509</v>
+        <v>-0.5312</v>
       </c>
       <c r="P25" t="n">
+        <v>-1.7855</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.1984</v>
       </c>
-      <c r="Q25" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.1903</v>
-      </c>
       <c r="S25" t="n">
-        <v>-1.4477</v>
+        <v>0.4435</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8728</v>
+        <v>0.3571</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5748</v>
+        <v>0.0864</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0675</v>
+        <v>-1.4724</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0675</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="26">
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3365</v>
+        <v>-4.6681</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.965</v>
+        <v>-1.5772</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.3715</v>
+        <v>-3.091</v>
       </c>
       <c r="G26" t="n">
         <v>-2.7377</v>
@@ -2478,13 +2478,13 @@
         <v>0.9919</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1191</v>
+        <v>-0.2125</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6859</v>
+        <v>0.0738</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5669</v>
+        <v>-0.2863</v>
       </c>
       <c r="V26" t="n">
         <v>0.266</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.249</v>
+        <v>-4.7763</v>
       </c>
       <c r="E27" t="n">
         <v>-4.12</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.129</v>
+        <v>-0.6563</v>
       </c>
       <c r="G27" t="n">
         <v>-3.3927</v>
@@ -2556,13 +2556,13 @@
         <v>1.3887</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3367</v>
+        <v>0.136</v>
       </c>
       <c r="T27" t="n">
         <v>-0.0056</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3311</v>
+        <v>0.1416</v>
       </c>
       <c r="V27" t="n">
         <v>0.0675</v>
@@ -2589,13 +2589,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.2161</v>
+        <v>-5.9279</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.4492</v>
+        <v>-2.2452</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.7669</v>
+        <v>-3.6827</v>
       </c>
       <c r="G28" t="n">
         <v>-4.0256</v>
@@ -2634,13 +2634,13 @@
         <v>0.3968</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.7261</v>
+        <v>-0.4379</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.238</v>
+        <v>-0.034</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.488</v>
+        <v>-0.4039</v>
       </c>
       <c r="V28" t="n">
         <v>-0.8692</v>
@@ -2667,19 +2667,19 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-29.7814</v>
+        <v>-27.0606</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.401100000000001</v>
+        <v>-2.4011</v>
       </c>
       <c r="F29" t="n">
-        <v>-27.3804</v>
+        <v>-24.6595</v>
       </c>
       <c r="G29" t="n">
         <v>-20.3922</v>
       </c>
       <c r="H29" t="n">
-        <v>-7.080900000000001</v>
+        <v>-7.0809</v>
       </c>
       <c r="I29" t="n">
         <v>-13.3113</v>
@@ -2703,7 +2703,7 @@
         <v>-13.8615</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.935400000000001</v>
+        <v>-7.9354</v>
       </c>
       <c r="Q29" t="n">
         <v>-18.8464</v>
@@ -2712,19 +2712,19 @@
         <v>10.9111</v>
       </c>
       <c r="S29" t="n">
-        <v>-5.073199999999999</v>
+        <v>-2.3524</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.6146</v>
+        <v>-1.6145</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.4584</v>
+        <v>-0.7377999999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>3.619599999999999</v>
+        <v>3.6196</v>
       </c>
       <c r="W29" t="n">
-        <v>6.6164</v>
+        <v>6.616400000000001</v>
       </c>
       <c r="X29" t="n">
         <v>-2.996700000000001</v>
